--- a/daily_matches/job_matches_2026-07-04.xlsx
+++ b/daily_matches/job_matches_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,70 +468,210 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>AI/LLM Engineer (ChatGPT &amp; Voice AI Agent Development)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Simpsocial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R</t>
+          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29d3e19caf513</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6f6a302d8c709e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>Castleton Commodities International</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, FastAPI, Git, Snowflake, Python</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76d085ea51c27f6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Group AI/ML Sol Architect - PostgreSQL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Databricks, Kafka, PostgreSQL, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WhiteWater Express Car Wash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, EC2, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85da536c77d90e54</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer / BI Developer (GCP, Power BI, Tableau)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Expleo Group</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Rochester, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>12.2</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, BigQuery, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33f34675d6b944c5</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b8537a55ac652d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst – Department of Human Services</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>El Paso County, CO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e25cff2764c2ef54</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-04.xlsx
+++ b/daily_matches/job_matches_2026-07-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/LLM Engineer (ChatGPT &amp; Voice AI Agent Development)</t>
+          <t>Commercial Analytics Engineer Business Decision Intelligence</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Simpsocial</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, PostgreSQL</t>
+          <t>RAG, Prompt Engineering, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6f6a302d8c709e</t>
+          <t>https://www.indeed.com/viewjob?jk=3722313cc0bbee22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Commercial Analytics Engineer - Go To Market Analytics</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Castleton Commodities International</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, FastAPI, Git, Snowflake, Python</t>
+          <t>RAG, Prompt Engineering, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d085ea51c27f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc07e359a2b1915</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Group AI/ML Sol Architect - PostgreSQL</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Databricks, Kafka, PostgreSQL, MySQL, Python</t>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
+          <t>https://www.indeed.com/viewjob?jk=02cd4ab61a45abcd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer III- Senior Associate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Terraform, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,77 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85da536c77d90e54</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer / BI Developer (GCP, Power BI, Tableau)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Expleo Group</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Rochester, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, BigQuery, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8537a55ac652d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst – Department of Human Services</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>El Paso County, CO</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e25cff2764c2ef54</t>
+          <t>https://www.indeed.com/viewjob?jk=84905d67c4b1248e</t>
         </is>
       </c>
     </row>
